--- a/CPU_Instruction_Set.xlsx
+++ b/CPU_Instruction_Set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Reyansh\CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7D2347-8BEA-4C1E-936A-3E9866144D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5DA4D1-2BA4-4B9E-A8EA-06FE0A6B256E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25FB4FC9-3870-4051-8B39-19FFBC5F0F37}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -56,20 +57,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t xml:space="preserve">add </t>
   </si>
   <si>
-    <t xml:space="preserve"> add DST, SRC </t>
-  </si>
-  <si>
     <t xml:space="preserve">sub </t>
   </si>
   <si>
-    <t xml:space="preserve"> sub DST, SRC </t>
-  </si>
-  <si>
     <t xml:space="preserve">inc </t>
   </si>
   <si>
@@ -91,21 +86,12 @@
     <t xml:space="preserve">and </t>
   </si>
   <si>
-    <t xml:space="preserve"> and DST, SRC </t>
-  </si>
-  <si>
     <t xml:space="preserve">or  </t>
   </si>
   <si>
-    <t xml:space="preserve"> or DST, SRC </t>
-  </si>
-  <si>
     <t xml:space="preserve">xor </t>
   </si>
   <si>
-    <t xml:space="preserve"> xor DST, SRC </t>
-  </si>
-  <si>
     <t xml:space="preserve">not </t>
   </si>
   <si>
@@ -124,24 +110,15 @@
     <t xml:space="preserve"> jmp LABEL </t>
   </si>
   <si>
-    <t xml:space="preserve"> Unconditional jump</t>
-  </si>
-  <si>
     <t xml:space="preserve">jz  </t>
   </si>
   <si>
     <t xml:space="preserve"> jz LABEL </t>
   </si>
   <si>
-    <t xml:space="preserve"> Jump if zero flag is set</t>
-  </si>
-  <si>
     <t>swp</t>
   </si>
   <si>
-    <t>swp REG1, REG2</t>
-  </si>
-  <si>
     <t>dbnxt</t>
   </si>
   <si>
@@ -160,12 +137,6 @@
     <t>str</t>
   </si>
   <si>
-    <t>ldr REG, SRC_REG</t>
-  </si>
-  <si>
-    <t>str REG, SRC_REG</t>
-  </si>
-  <si>
     <t>Operation</t>
   </si>
   <si>
@@ -209,6 +180,54 @@
   </si>
   <si>
     <t xml:space="preserve"> Two’s-complement negation and store the result in DST</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>Only the first bit is used to identify this opcode. The remaining 15 bits specify the address of the label for jumps.</t>
+  </si>
+  <si>
+    <t>label ADD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unconditional jump to the address specified in the following instruction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jump if zero flag is set to the address specified in the following instruction.</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>NOT TO BE USED</t>
+  </si>
+  <si>
+    <t>This is to stop a command from happening. Useful on dbnxt or anything that needs multiple lines to define fully.</t>
+  </si>
+  <si>
+    <t>ldr REG SRC_REG</t>
+  </si>
+  <si>
+    <t>str REG SRC_REG</t>
+  </si>
+  <si>
+    <t>swp REG1 REG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> add DST SRC </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sub DST SRC </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> and DST SRC </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> or DST SRC </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> xor DST SRC </t>
   </si>
 </sst>
 </file>
@@ -569,83 +588,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90AD4DA6-00CD-42D1-A825-ADAFAC8D9691}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="72.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="str" cm="1">
-        <f t="array" ref="B2:B21">_xlfn.BASE(_xlfn.SEQUENCE(20,1,0),2,5)</f>
+        <f t="array" ref="B2:B33">_xlfn.BASE(_xlfn.SEQUENCE(32,1,0),2,5)</f>
         <v>00000</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="str">
         <v>00001</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="str">
         <v>00010</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="str">
         <v>00011</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -656,169 +675,178 @@
         <v>00100</v>
       </c>
       <c r="C6" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="str">
         <v>00101</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" t="str">
         <v>00110</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="str">
         <v>00111</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" t="str">
         <v>01000</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11" t="str">
         <v>01001</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B12" t="str">
         <v>01010</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B13" t="str">
         <v>01011</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B14" t="str">
         <v>01100</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B15" t="str">
         <v>01101</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B16" t="str">
         <v>01110</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B17" t="str">
         <v>01111</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
       <c r="B18" t="str">
         <v>10000</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -834,6 +862,75 @@
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B21" t="str">
         <v>10011</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B22" t="str">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B23" t="str">
+        <v>10101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" t="str">
+        <v>10110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B25" t="str">
+        <v>10111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26" t="str">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" t="str">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B28" t="str">
+        <v>11010</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B29" t="str">
+        <v>11011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B30" t="str">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B31" t="str">
+        <v>11101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B32" t="str">
+        <v>11110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="str">
+        <v>11111</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/CPU_Instruction_Set.xlsx
+++ b/CPU_Instruction_Set.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Reyansh\CPU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Reyansh\BOLT-16_CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5DA4D1-2BA4-4B9E-A8EA-06FE0A6B256E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080887A5-803C-469D-A17D-E9D34E1096DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25FB4FC9-3870-4051-8B39-19FFBC5F0F37}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,52 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
-  <si>
-    <t xml:space="preserve">add </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sub </t>
-  </si>
-  <si>
-    <t xml:space="preserve">inc </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> inc DST </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Increment DST by 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dec </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> dec DST </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Decrement DST by 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and </t>
-  </si>
-  <si>
-    <t xml:space="preserve">or  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xor </t>
-  </si>
-  <si>
-    <t xml:space="preserve">not </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> not DST </t>
-  </si>
-  <si>
-    <t xml:space="preserve">neg </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> neg DST </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
   <si>
     <t xml:space="preserve">jmp </t>
   </si>
@@ -110,21 +64,12 @@
     <t xml:space="preserve"> jmp LABEL </t>
   </si>
   <si>
-    <t xml:space="preserve">jz  </t>
-  </si>
-  <si>
     <t xml:space="preserve"> jz LABEL </t>
   </si>
   <si>
     <t>swp</t>
   </si>
   <si>
-    <t>dbnxt</t>
-  </si>
-  <si>
-    <t>dbnxt REG</t>
-  </si>
-  <si>
     <t>end</t>
   </si>
   <si>
@@ -161,51 +106,12 @@
     <t>Swap the values of REG1 and REG2</t>
   </si>
   <si>
-    <t xml:space="preserve"> Add SRC to DST and store the result in DST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Subtract SRC from DST and store the result in DST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bitwise AND and store the result in DST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bitwise OR and store the result in DST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bitwise XOR and store the result in DST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bitwise NOT and store the result in DST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Two’s-complement negation and store the result in DST</t>
-  </si>
-  <si>
     <t>label</t>
   </si>
   <si>
-    <t>Only the first bit is used to identify this opcode. The remaining 15 bits specify the address of the label for jumps.</t>
-  </si>
-  <si>
-    <t>label ADD</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Unconditional jump to the address specified in the following instruction.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Jump if zero flag is set to the address specified in the following instruction.</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>NOT TO BE USED</t>
-  </si>
-  <si>
-    <t>This is to stop a command from happening. Useful on dbnxt or anything that needs multiple lines to define fully.</t>
-  </si>
-  <si>
     <t>ldr REG SRC_REG</t>
   </si>
   <si>
@@ -215,19 +121,172 @@
     <t>swp REG1 REG2</t>
   </si>
   <si>
-    <t xml:space="preserve"> add DST SRC </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> sub DST SRC </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and DST SRC </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> or DST SRC </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> xor DST SRC </t>
+    <t>add</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>xor</t>
+  </si>
+  <si>
+    <t>not</t>
+  </si>
+  <si>
+    <t>neg</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>mul</t>
+  </si>
+  <si>
+    <t>div</t>
+  </si>
+  <si>
+    <t>inc</t>
+  </si>
+  <si>
+    <t>dec</t>
+  </si>
+  <si>
+    <t>shl</t>
+  </si>
+  <si>
+    <t>shr</t>
+  </si>
+  <si>
+    <t>Shift left</t>
+  </si>
+  <si>
+    <t>Shift right</t>
+  </si>
+  <si>
+    <t>cmp</t>
+  </si>
+  <si>
+    <t>sar</t>
+  </si>
+  <si>
+    <t>ror</t>
+  </si>
+  <si>
+    <t>Shift right arithmetic</t>
+  </si>
+  <si>
+    <t>Rotate right</t>
+  </si>
+  <si>
+    <t>Jump to the address specified in the following instruction if the output of the previous operation was 0.</t>
+  </si>
+  <si>
+    <t>jz</t>
+  </si>
+  <si>
+    <t>arithmetic</t>
+  </si>
+  <si>
+    <t>arithmetic OP FLAGS</t>
+  </si>
+  <si>
+    <t>Chooses an arithmetic operation (table on the right) and executes it using the flags specified.</t>
+  </si>
+  <si>
+    <t>Compare</t>
+  </si>
+  <si>
+    <t>Decrement</t>
+  </si>
+  <si>
+    <t>Increment</t>
+  </si>
+  <si>
+    <t>Divide</t>
+  </si>
+  <si>
+    <t>Multiply</t>
+  </si>
+  <si>
+    <t>Subtract</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>Negate</t>
+  </si>
+  <si>
+    <t>Not</t>
+  </si>
+  <si>
+    <t>Bitwise XOR</t>
+  </si>
+  <si>
+    <t>Bitwise OR</t>
+  </si>
+  <si>
+    <t>Bitwise AND</t>
+  </si>
+  <si>
+    <t>db</t>
+  </si>
+  <si>
+    <t>db REG</t>
+  </si>
+  <si>
+    <t>The defined name of this label will be stored in the compiler variables.</t>
+  </si>
+  <si>
+    <t>and DST SRC</t>
+  </si>
+  <si>
+    <t>or DST SRC</t>
+  </si>
+  <si>
+    <t>xor DST SRC</t>
+  </si>
+  <si>
+    <t>cmp DST SRC</t>
+  </si>
+  <si>
+    <t>not DST</t>
+  </si>
+  <si>
+    <t>neg DST</t>
+  </si>
+  <si>
+    <t>add DST</t>
+  </si>
+  <si>
+    <t>sub DST</t>
+  </si>
+  <si>
+    <t>mul DST</t>
+  </si>
+  <si>
+    <t>div DST</t>
+  </si>
+  <si>
+    <t>inc DST</t>
+  </si>
+  <si>
+    <t>dec DST</t>
+  </si>
+  <si>
+    <t>shl DST DIST</t>
+  </si>
+  <si>
+    <t>shr DST DIST</t>
+  </si>
+  <si>
+    <t>ror DST DIST</t>
+  </si>
+  <si>
+    <t>sar DST DIST</t>
   </si>
 </sst>
 </file>
@@ -588,349 +647,311 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90AD4DA6-00CD-42D1-A825-ADAFAC8D9691}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="93.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="str" cm="1">
-        <f t="array" ref="B2:B33">_xlfn.BASE(_xlfn.SEQUENCE(32,1,0),2,5)</f>
+        <f t="array" ref="B2:B9">_xlfn.BASE(_xlfn.SEQUENCE(8,1,0),2,5)</f>
         <v>00000</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="str">
         <v>00001</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1" t="str">
         <v>00010</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
         <v>00011</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B6" t="str">
         <v>00100</v>
       </c>
       <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="str">
         <v>00101</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B8" t="str">
         <v>00110</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>5</v>
       </c>
       <c r="B9" t="str">
         <v>00111</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="str">
-        <v>01000</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>10000</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="str">
-        <v>01001</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="I14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H15" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="str">
-        <v>01010</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="I15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="str">
-        <v>01011</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>01100</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="I16" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="str">
-        <v>01101</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="str">
-        <v>01110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="str">
-        <v>01111</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" t="str">
-        <v>10000</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B19" t="str">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B20" t="str">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B21" t="str">
-        <v>10011</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B22" t="str">
-        <v>10100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B23" t="str">
-        <v>10101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B24" t="str">
-        <v>10110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B25" t="str">
-        <v>10111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B26" t="str">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B27" t="str">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B28" t="str">
-        <v>11010</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B29" t="str">
-        <v>11011</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B30" t="str">
-        <v>11100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B31" t="str">
-        <v>11101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B32" t="str">
-        <v>11110</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="str">
-        <v>11111</v>
-      </c>
-      <c r="C33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" t="s">
-        <v>48</v>
+      <c r="J16" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/CPU_Instruction_Set.xlsx
+++ b/CPU_Instruction_Set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Reyansh\BOLT-16_CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080887A5-803C-469D-A17D-E9D34E1096DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5D23B8-227E-474B-B6A7-FF711DFCAE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25FB4FC9-3870-4051-8B39-19FFBC5F0F37}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -685,7 +685,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="str" cm="1">
-        <f t="array" ref="B2:B9">_xlfn.BASE(_xlfn.SEQUENCE(8,1,0),2,5)</f>
+        <f t="array" ref="B2:B10">_xlfn.BASE(_xlfn.SEQUENCE(9,1,0),2,5)</f>
         <v>00000</v>
       </c>
       <c r="C2" t="s">
@@ -866,6 +866,18 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="str">
+        <v>01000</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
       <c r="H10" t="s">
         <v>30</v>
       </c>
@@ -899,18 +911,6 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13">
-        <v>10000</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
       <c r="H13" t="s">
         <v>33</v>
       </c>
